--- a/artfynd/A 23730-2025 artfynd.xlsx
+++ b/artfynd/A 23730-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125852456</v>
+        <v>125852458</v>
       </c>
       <c r="B2" t="n">
-        <v>91238</v>
+        <v>91245</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>451217</v>
+        <v>451166</v>
       </c>
       <c r="R2" t="n">
-        <v>7057372</v>
+        <v>7057417</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125852458</v>
+        <v>125852456</v>
       </c>
       <c r="B3" t="n">
-        <v>91238</v>
+        <v>91245</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>451166</v>
+        <v>451217</v>
       </c>
       <c r="R3" t="n">
-        <v>7057417</v>
+        <v>7057372</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>

--- a/artfynd/A 23730-2025 artfynd.xlsx
+++ b/artfynd/A 23730-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125852458</v>
       </c>
       <c r="B2" t="n">
-        <v>91245</v>
+        <v>91246</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>125852456</v>
       </c>
       <c r="B3" t="n">
-        <v>91245</v>
+        <v>91246</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 23730-2025 artfynd.xlsx
+++ b/artfynd/A 23730-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125852458</v>
       </c>
       <c r="B2" t="n">
-        <v>91246</v>
+        <v>91250</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>125852456</v>
       </c>
       <c r="B3" t="n">
-        <v>91246</v>
+        <v>91250</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 23730-2025 artfynd.xlsx
+++ b/artfynd/A 23730-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125852458</v>
       </c>
       <c r="B2" t="n">
-        <v>91250</v>
+        <v>91252</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>125852456</v>
       </c>
       <c r="B3" t="n">
-        <v>91250</v>
+        <v>91252</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>125852438</v>
       </c>
       <c r="B4" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 23730-2025 artfynd.xlsx
+++ b/artfynd/A 23730-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125852458</v>
       </c>
       <c r="B2" t="n">
-        <v>91252</v>
+        <v>91254</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>125852456</v>
       </c>
       <c r="B3" t="n">
-        <v>91252</v>
+        <v>91254</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 23730-2025 artfynd.xlsx
+++ b/artfynd/A 23730-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125852458</v>
       </c>
       <c r="B2" t="n">
-        <v>91254</v>
+        <v>91256</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>125852456</v>
       </c>
       <c r="B3" t="n">
-        <v>91254</v>
+        <v>91256</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 23730-2025 artfynd.xlsx
+++ b/artfynd/A 23730-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125852458</v>
       </c>
       <c r="B2" t="n">
-        <v>91256</v>
+        <v>91260</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>125852456</v>
       </c>
       <c r="B3" t="n">
-        <v>91256</v>
+        <v>91260</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>125852438</v>
       </c>
       <c r="B4" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 23730-2025 artfynd.xlsx
+++ b/artfynd/A 23730-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125852458</v>
+        <v>125852456</v>
       </c>
       <c r="B2" t="n">
         <v>91260</v>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>451166</v>
+        <v>451217</v>
       </c>
       <c r="R2" t="n">
-        <v>7057417</v>
+        <v>7057372</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,7 +772,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125852456</v>
+        <v>125852458</v>
       </c>
       <c r="B3" t="n">
         <v>91260</v>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>451217</v>
+        <v>451166</v>
       </c>
       <c r="R3" t="n">
-        <v>7057372</v>
+        <v>7057417</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>

--- a/artfynd/A 23730-2025 artfynd.xlsx
+++ b/artfynd/A 23730-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125852456</v>
+        <v>125852458</v>
       </c>
       <c r="B2" t="n">
         <v>91260</v>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>451217</v>
+        <v>451166</v>
       </c>
       <c r="R2" t="n">
-        <v>7057372</v>
+        <v>7057417</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,7 +772,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125852458</v>
+        <v>125852456</v>
       </c>
       <c r="B3" t="n">
         <v>91260</v>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>451166</v>
+        <v>451217</v>
       </c>
       <c r="R3" t="n">
-        <v>7057417</v>
+        <v>7057372</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>

--- a/artfynd/A 23730-2025 artfynd.xlsx
+++ b/artfynd/A 23730-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125852458</v>
       </c>
       <c r="B2" t="n">
-        <v>91260</v>
+        <v>91263</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>125852456</v>
       </c>
       <c r="B3" t="n">
-        <v>91260</v>
+        <v>91263</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>125852438</v>
       </c>
       <c r="B4" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
